--- a/artfynd/A 21821-2026 artfynd.xlsx
+++ b/artfynd/A 21821-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,41 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69557913</v>
+        <v>3856420</v>
       </c>
       <c r="B2" t="n">
-        <v>106348</v>
+        <v>106415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221447</v>
+        <v>698</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Sen fältgentiana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
+          <t>Gentianella campestris var. campestris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N om Östra Syninge, Upl</t>
+          <t>Östra Syninge, 700 m NNV om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>697396</v>
       </c>
       <c r="R2" t="n">
-        <v>6629759</v>
+        <v>6629739</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Upplandsfloran - detaljuppgifter. 75 ex</t>
+          <t>75 ex i enbevuxen naturbetesmark, friskängar. Välhävdat av tre hästar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,21 +771,245 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Enbevuxen naturbetesmark, friskängar, Välhävdat av tre hästar</t>
+          <t>Naturbetesmark (häst)</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri AB-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>16831142</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106415</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>698</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sen fältgentiana</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Gentianella campestris var. campestris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Östra Syninge, 700 m NNV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>697388</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6629731</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Husby-Sjuhundra</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2014-08-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2014-08-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Endast ett blommande ex vid RN 6629627, 1652247. Frisk lågörtäng med Briza, Nardus, Sesleria caerule, Succisa pratensis (mycket riklig)  mm. Området extensivt fårbetat.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Naturbetesmark, glest enbevuxen. Friskängar, extensivt fårbetade</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>69557913</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106494</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fältgentiana</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>N om Östra Syninge, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>697396</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6629759</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Husby-Sjuhundra</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2001-01-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2001-12-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter. 75 ex</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Enbevuxen naturbetesmark, friskängar, Välhävdat av tre hästar</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Mora Aronsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Joakim Ekman</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Upplands Flora 2010</t>
         </is>

--- a/artfynd/A 21821-2026 artfynd.xlsx
+++ b/artfynd/A 21821-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
           <t>Floraväkteri AB-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3856420</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16831142</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,8 +1029,18 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69557913</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>